--- a/Excel/CompositeConfig.xlsx
+++ b/Excel/CompositeConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1078" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="395">
   <si>
     <t>Id</t>
   </si>
@@ -1111,13 +1111,13 @@
     <t>极雀神器</t>
   </si>
   <si>
+    <t>4058,4111</t>
+  </si>
+  <si>
+    <t>极玄神器</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>4058,4111</t>
-  </si>
-  <si>
-    <t>极玄神器</t>
   </si>
   <si>
     <t>4059,4111</t>
@@ -7101,12 +7101,6 @@
       </c>
     </row>
     <row r="163" customHeight="1" spans="1:12">
-      <c r="A163" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="B163" s="1" t="s">
-        <v>359</v>
-      </c>
       <c r="C163" s="1">
         <v>514</v>
       </c>
@@ -7117,7 +7111,7 @@
         <v>325</v>
       </c>
       <c r="F163" s="5" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G163" s="5" t="s">
         <v>353</v>
@@ -7126,7 +7120,7 @@
         <v>18</v>
       </c>
       <c r="I163" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="J163" s="1">
         <v>50</v>
@@ -7140,10 +7134,10 @@
     </row>
     <row r="164" customHeight="1" spans="1:12">
       <c r="A164" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C164" s="1">
         <v>515</v>
